--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.38146705986954</v>
+        <v>5.261988397228801</v>
       </c>
       <c r="D2" t="n">
-        <v>28.83305340556822</v>
+        <v>4.685371178404837</v>
       </c>
       <c r="E2" t="n">
-        <v>10.19533755809139</v>
+        <v>1.656742353189851</v>
       </c>
       <c r="F2" t="n">
-        <v>13.64710193532815</v>
+        <v>2.217654064490824</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.53399277446253</v>
+        <v>4.636773825850161</v>
       </c>
       <c r="D3" t="n">
-        <v>19.85789158508228</v>
+        <v>3.226907382575871</v>
       </c>
       <c r="E3" t="n">
-        <v>10.19533755809139</v>
+        <v>1.656742353189851</v>
       </c>
       <c r="F3" t="n">
-        <v>13.64710193532815</v>
+        <v>2.217654064490824</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.82815845430918</v>
+        <v>2.247075748825242</v>
       </c>
       <c r="D4" t="n">
-        <v>5.562625259521195</v>
+        <v>0.9039266046721943</v>
       </c>
       <c r="E4" t="n">
-        <v>10.19533755809139</v>
+        <v>1.656742353189851</v>
       </c>
       <c r="F4" t="n">
-        <v>13.64710193532815</v>
+        <v>2.217654064490824</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.07795440050668</v>
+        <v>5.050167590082336</v>
       </c>
       <c r="D5" t="n">
-        <v>31.2941431051959</v>
+        <v>5.085298254594333</v>
       </c>
       <c r="E5" t="n">
-        <v>10.19533755809139</v>
+        <v>1.656742353189851</v>
       </c>
       <c r="F5" t="n">
-        <v>13.64710193532815</v>
+        <v>2.217654064490824</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.16304707604753</v>
+        <v>8.476495149857723</v>
       </c>
       <c r="D6" t="n">
-        <v>52.22292795362615</v>
+        <v>8.48622579246425</v>
       </c>
       <c r="E6" t="n">
-        <v>10.19533755809139</v>
+        <v>1.656742353189851</v>
       </c>
       <c r="F6" t="n">
-        <v>13.64710193532815</v>
+        <v>2.217654064490824</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.86940937065877</v>
+        <v>5.17877902273205</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9676882306284</v>
+        <v>5.194749337477115</v>
       </c>
       <c r="E7" t="n">
-        <v>10.19533755809139</v>
+        <v>1.656742353189851</v>
       </c>
       <c r="F7" t="n">
-        <v>13.64710193532815</v>
+        <v>2.217654064490824</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.17030973519045</v>
+        <v>4.740175331968449</v>
       </c>
       <c r="D8" t="n">
-        <v>6.580202987995753</v>
+        <v>1.06928298554931</v>
       </c>
       <c r="E8" t="n">
-        <v>10.19533755809139</v>
+        <v>1.656742353189851</v>
       </c>
       <c r="F8" t="n">
-        <v>13.64710193532815</v>
+        <v>2.217654064490824</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.43315152309303</v>
+        <v>4.457887122502617</v>
       </c>
       <c r="D9" t="n">
-        <v>27.20926356754182</v>
+        <v>4.421505329725545</v>
       </c>
       <c r="E9" t="n">
-        <v>10.19533755809139</v>
+        <v>1.656742353189851</v>
       </c>
       <c r="F9" t="n">
-        <v>13.64710193532815</v>
+        <v>2.217654064490824</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.04992430923028</v>
+        <v>2.770612700249921</v>
       </c>
       <c r="D10" t="n">
-        <v>15.64041801669512</v>
+        <v>2.541567927712957</v>
       </c>
       <c r="E10" t="n">
-        <v>10.19533755809139</v>
+        <v>1.656742353189851</v>
       </c>
       <c r="F10" t="n">
-        <v>13.64710193532815</v>
+        <v>2.217654064490824</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
